--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_3/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9694,0.0015,0.0077,0.0034</t>
-  </si>
-  <si>
-    <t>0.9608,0.0003,0.0007,0.0368</t>
-  </si>
-  <si>
-    <t>0.9338,0.0030,0.0069,0.0338</t>
-  </si>
-  <si>
-    <t>0.9350,0.0008,0.0039,0.0343</t>
-  </si>
-  <si>
-    <t>0.9685,0.0013,0.0011,0.0183</t>
-  </si>
-  <si>
-    <t>0.7957,0.0025,0.0016,0.2863</t>
-  </si>
-  <si>
-    <t>0.7884,0.0112,0.0131,0.2113</t>
-  </si>
-  <si>
-    <t>0.9018,0.0033,0.0029,0.0971</t>
-  </si>
-  <si>
-    <t>0.7873,0.0016,0.0014,0.3239</t>
-  </si>
-  <si>
-    <t>0.9701,0.0021,0.0009,0.0139</t>
-  </si>
-  <si>
-    <t>0.8259,0.0128,0.0044,0.0685</t>
-  </si>
-  <si>
-    <t>0.9525,0.0034,0.0012,0.0205</t>
-  </si>
-  <si>
-    <t>0.9666,0.0017,0.0260,0.0006</t>
-  </si>
-  <si>
-    <t>0.8989,0.0037,0.1373,0.0013</t>
-  </si>
-  <si>
-    <t>0.8484,0.0077,0.2691,0.0011</t>
-  </si>
-  <si>
-    <t>0.9202,0.0058,0.1017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9725,0.0013,0.0050,0.0037</t>
-  </si>
-  <si>
-    <t>0.9164,0.0488,0.0094,0.0006</t>
-  </si>
-  <si>
-    <t>0.9183,0.0384,0.0187,0.0007</t>
-  </si>
-  <si>
-    <t>0.9379,0.0157,0.0075,0.0049</t>
-  </si>
-  <si>
-    <t>0.7147,0.1548,0.0590,0.0019</t>
-  </si>
-  <si>
-    <t>0.9708,0.0039,0.0109,0.0009</t>
-  </si>
-  <si>
-    <t>0.9106,0.0019,0.0949,0.0016</t>
-  </si>
-  <si>
-    <t>0.9872,0.0004,0.0086,0.0002</t>
-  </si>
-  <si>
-    <t>0.1610,0.0044,0.9183,0.0007</t>
-  </si>
-  <si>
-    <t>0.9741,0.0004,0.0082,0.0016</t>
-  </si>
-  <si>
-    <t>0.9493,0.0008,0.0688,0.0005</t>
-  </si>
-  <si>
-    <t>0.3524,0.0015,0.8723,0.0002</t>
-  </si>
-  <si>
-    <t>0.1171,0.0032,0.9485,0.0003</t>
-  </si>
-  <si>
-    <t>0.7904,0.1369,0.0486,0.0069</t>
-  </si>
-  <si>
-    <t>0.9648,0.0074,0.0075,0.0028</t>
-  </si>
-  <si>
-    <t>0.3057,0.3077,0.5124,0.0112</t>
-  </si>
-  <si>
-    <t>0.8718,0.0226,0.1063,0.0011</t>
-  </si>
-  <si>
-    <t>0.8598,0.0400,0.0320,0.0147</t>
-  </si>
-  <si>
-    <t>0.3365,0.0134,0.6849,0.0252</t>
-  </si>
-  <si>
-    <t>0.9728,0.0039,0.0059,0.0031</t>
-  </si>
-  <si>
-    <t>0.8629,0.0394,0.0440,0.0079</t>
-  </si>
-  <si>
-    <t>0.1516,0.1597,0.7267,0.0197</t>
-  </si>
-  <si>
-    <t>0.5668,0.0031,0.5955,0.0012</t>
-  </si>
-  <si>
-    <t>0.8641,0.0040,0.2048,0.0003</t>
-  </si>
-  <si>
-    <t>0.8753,0.0005,0.1087,0.0017</t>
-  </si>
-  <si>
-    <t>0.6333,0.0149,0.5355,0.0018</t>
-  </si>
-  <si>
-    <t>0.1456,0.7868,0.1610,0.0011</t>
-  </si>
-  <si>
-    <t>0.3904,0.0165,0.7241,0.0039</t>
-  </si>
-  <si>
-    <t>0.9067,0.0102,0.0351,0.0115</t>
-  </si>
-  <si>
-    <t>0.9656,0.0085,0.0045,0.0016</t>
-  </si>
-  <si>
-    <t>0.9864,0.0033,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9515,0.0354,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.5638,0.0051,0.6762,0.0004</t>
-  </si>
-  <si>
-    <t>0.0607,0.0459,0.9589,0.0007</t>
-  </si>
-  <si>
-    <t>0.8980,0.0032,0.1722,0.0006</t>
-  </si>
-  <si>
-    <t>0.5090,0.0041,0.6235,0.0020</t>
-  </si>
-  <si>
-    <t>0.0759,0.0887,0.9130,0.0013</t>
-  </si>
-  <si>
-    <t>0.0969,0.2300,0.9319,0.0026</t>
-  </si>
-  <si>
-    <t>0.9694,0.0029,0.0004,0.0098</t>
-  </si>
-  <si>
-    <t>0.7526,0.0115,0.0092,0.2052</t>
-  </si>
-  <si>
-    <t>0.9337,0.0125,0.0103,0.0149</t>
-  </si>
-  <si>
-    <t>0.4104,0.1467,0.5791,0.0199</t>
-  </si>
-  <si>
-    <t>0.9086,0.0015,0.0018,0.1092</t>
-  </si>
-  <si>
-    <t>0.9591,0.0009,0.0011,0.0347</t>
-  </si>
-  <si>
-    <t>0.9819,0.0023,0.0011,0.0036</t>
-  </si>
-  <si>
-    <t>0.1057,0.1141,0.9160,0.0005</t>
-  </si>
-  <si>
-    <t>0.2162,0.0144,0.9328,0.0002</t>
-  </si>
-  <si>
-    <t>0.3551,0.0159,0.7701,0.0010</t>
-  </si>
-  <si>
-    <t>0.0327,0.1254,0.9763,0.0010</t>
-  </si>
-  <si>
-    <t>0.2369,0.0041,0.9101,0.0001</t>
-  </si>
-  <si>
-    <t>0.9216,0.0477,0.0136,0.0022</t>
-  </si>
-  <si>
-    <t>0.0529,0.9745,0.0033,0.0001</t>
-  </si>
-  <si>
-    <t>0.9484,0.0013,0.0705,0.0010</t>
-  </si>
-  <si>
-    <t>0.9924,0.0004,0.0018,0.0003</t>
-  </si>
-  <si>
-    <t>0.0612,0.0335,0.9520,0.0011</t>
-  </si>
-  <si>
-    <t>0.8376,0.0213,0.2083,0.0008</t>
-  </si>
-  <si>
-    <t>0.9732,0.0016,0.0228,0.0002</t>
-  </si>
-  <si>
-    <t>0.0778,0.7872,0.6261,0.0067</t>
-  </si>
-  <si>
-    <t>0.0725,0.5850,0.7652,0.0005</t>
-  </si>
-  <si>
-    <t>0.7204,0.0018,0.0219,0.1789</t>
-  </si>
-  <si>
-    <t>0.5015,0.0002,0.0007,0.7996</t>
-  </si>
-  <si>
-    <t>0.6004,0.0011,0.0037,0.5563</t>
-  </si>
-  <si>
-    <t>0.8902,0.0003,0.0010,0.1636</t>
-  </si>
-  <si>
-    <t>0.8452,0.0005,0.0016,0.2198</t>
-  </si>
-  <si>
-    <t>0.9544,0.0002,0.0003,0.0697</t>
-  </si>
-  <si>
-    <t>0.0437,0.1334,0.9757,0.0003</t>
-  </si>
-  <si>
-    <t>0.0335,0.0560,0.9799,0.0004</t>
-  </si>
-  <si>
-    <t>0.6563,0.0114,0.5476,0.0004</t>
-  </si>
-  <si>
-    <t>0.2452,0.2038,0.7230,0.0038</t>
-  </si>
-  <si>
-    <t>0.2901,0.2510,0.5583,0.0008</t>
-  </si>
-  <si>
-    <t>0.4975,0.0441,0.6706,0.0013</t>
-  </si>
-  <si>
-    <t>0.9343,0.0056,0.0041,0.0436</t>
-  </si>
-  <si>
-    <t>0.9612,0.0063,0.0021,0.0069</t>
-  </si>
-  <si>
-    <t>0.9582,0.0041,0.0007,0.0131</t>
-  </si>
-  <si>
-    <t>0.9432,0.0020,0.0016,0.0522</t>
-  </si>
-  <si>
-    <t>0.9732,0.0001,0.0001,0.0411</t>
-  </si>
-  <si>
-    <t>0.8146,0.0030,0.0053,0.2240</t>
-  </si>
-  <si>
-    <t>0.8804,0.0087,0.0037,0.0608</t>
-  </si>
-  <si>
-    <t>0.9282,0.0076,0.0053,0.0305</t>
-  </si>
-  <si>
-    <t>0.9868,0.0005,0.0005,0.0072</t>
-  </si>
-  <si>
-    <t>0.9428,0.0027,0.0039,0.0445</t>
-  </si>
-  <si>
-    <t>0.9767,0.0006,0.0001,0.0176</t>
-  </si>
-  <si>
-    <t>0.9138,0.0024,0.0024,0.0910</t>
-  </si>
-  <si>
-    <t>0.9311,0.0023,0.0011,0.0788</t>
-  </si>
-  <si>
-    <t>0.8932,0.0185,0.0039,0.0233</t>
-  </si>
-  <si>
-    <t>0.9651,0.0014,0.0003,0.0210</t>
-  </si>
-  <si>
-    <t>0.9040,0.0018,0.0028,0.1413</t>
-  </si>
-  <si>
-    <t>0.0227,0.0072,0.9927,0.0002</t>
-  </si>
-  <si>
-    <t>0.8466,0.0023,0.2182,0.0014</t>
-  </si>
-  <si>
-    <t>0.9833,0.0003,0.0062,0.0010</t>
-  </si>
-  <si>
-    <t>0.9104,0.0003,0.1466,0.0003</t>
-  </si>
-  <si>
-    <t>0.7375,0.1813,0.0159,0.0053</t>
-  </si>
-  <si>
-    <t>0.7350,0.1893,0.0253,0.0093</t>
-  </si>
-  <si>
-    <t>0.8417,0.1302,0.0085,0.0026</t>
-  </si>
-  <si>
-    <t>0.9337,0.0221,0.0095,0.0037</t>
-  </si>
-  <si>
-    <t>0.8405,0.0885,0.0226,0.0038</t>
-  </si>
-  <si>
-    <t>0.5951,0.3279,0.0774,0.0070</t>
-  </si>
-  <si>
-    <t>0.9329,0.0086,0.0155,0.0078</t>
-  </si>
-  <si>
-    <t>0.9423,0.0032,0.0234,0.0082</t>
-  </si>
-  <si>
-    <t>0.8755,0.0067,0.1866,0.0009</t>
-  </si>
-  <si>
-    <t>0.9919,0.0006,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.9898,0.0007,0.0043,0.0007</t>
-  </si>
-  <si>
-    <t>0.6611,0.0031,0.0355,0.1686</t>
-  </si>
-  <si>
-    <t>0.9908,0.0025,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9676,0.0174,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.7405,0.1085,0.1248,0.0043</t>
-  </si>
-  <si>
-    <t>0.6207,0.3650,0.0349,0.0005</t>
-  </si>
-  <si>
-    <t>0.9231,0.0120,0.0200,0.0066</t>
-  </si>
-  <si>
-    <t>0.7839,0.0503,0.0596,0.0514</t>
-  </si>
-  <si>
-    <t>0.7101,0.0976,0.0467,0.0326</t>
-  </si>
-  <si>
-    <t>0.9832,0.0023,0.0026,0.0020</t>
-  </si>
-  <si>
-    <t>0.9811,0.0003,0.0003,0.0143</t>
-  </si>
-  <si>
-    <t>0.9389,0.0021,0.0018,0.0413</t>
-  </si>
-  <si>
-    <t>0.9863,0.0008,0.0005,0.0048</t>
-  </si>
-  <si>
-    <t>0.9548,0.0045,0.0014,0.0153</t>
-  </si>
-  <si>
-    <t>0.9896,0.0010,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.8761,0.0073,0.0067,0.0749</t>
-  </si>
-  <si>
-    <t>0.9656,0.0025,0.0037,0.0105</t>
-  </si>
-  <si>
-    <t>0.0690,0.1990,0.9272,0.0007</t>
-  </si>
-  <si>
-    <t>0.7891,0.0436,0.1401,0.0025</t>
-  </si>
-  <si>
-    <t>0.6938,0.0271,0.3725,0.0024</t>
-  </si>
-  <si>
-    <t>0.6785,0.0048,0.5641,0.0003</t>
-  </si>
-  <si>
-    <t>0.9730,0.0010,0.0103,0.0011</t>
-  </si>
-  <si>
-    <t>0.9597,0.0013,0.0536,0.0006</t>
-  </si>
-  <si>
-    <t>0.8769,0.0014,0.0921,0.0041</t>
-  </si>
-  <si>
-    <t>0.9929,0.0002,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.8898,0.0025,0.0052,0.0955</t>
-  </si>
-  <si>
-    <t>0.0874,0.0011,0.0027,0.9714</t>
-  </si>
-  <si>
-    <t>0.5181,0.0003,0.0055,0.4895</t>
-  </si>
-  <si>
-    <t>0.9405,0.0003,0.0024,0.0432</t>
-  </si>
-  <si>
-    <t>0.3009,0.6824,0.0441,0.0006</t>
-  </si>
-  <si>
-    <t>0.9739,0.0009,0.0003,0.0168</t>
-  </si>
-  <si>
-    <t>0.9114,0.0336,0.0139,0.0055</t>
-  </si>
-  <si>
-    <t>0.9756,0.0008,0.0017,0.0113</t>
-  </si>
-  <si>
-    <t>0.7761,0.0745,0.0448,0.0206</t>
-  </si>
-  <si>
-    <t>0.9877,0.0005,0.0008,0.0040</t>
-  </si>
-  <si>
-    <t>0.9640,0.0017,0.0052,0.0153</t>
-  </si>
-  <si>
-    <t>0.9584,0.0027,0.0023,0.0158</t>
-  </si>
-  <si>
-    <t>0.2202,0.1922,0.8330,0.0438</t>
-  </si>
-  <si>
-    <t>0.7110,0.0015,0.0067,0.3515</t>
-  </si>
-  <si>
-    <t>0.8737,0.0016,0.0044,0.1235</t>
-  </si>
-  <si>
-    <t>0.9810,0.0023,0.0058,0.0008</t>
-  </si>
-  <si>
-    <t>0.9855,0.0004,0.0024,0.0014</t>
-  </si>
-  <si>
-    <t>0.9906,0.0006,0.0026,0.0004</t>
-  </si>
-  <si>
-    <t>0.9841,0.0027,0.0029,0.0006</t>
-  </si>
-  <si>
-    <t>0.9791,0.0033,0.0080,0.0007</t>
-  </si>
-  <si>
-    <t>0.9823,0.0011,0.0062,0.0012</t>
-  </si>
-  <si>
-    <t>0.8369,0.0140,0.0023,0.0542</t>
-  </si>
-  <si>
-    <t>0.9605,0.0027,0.0035,0.0271</t>
-  </si>
-  <si>
-    <t>0.9256,0.0063,0.0107,0.0264</t>
-  </si>
-  <si>
-    <t>0.9044,0.0010,0.0012,0.1124</t>
-  </si>
-  <si>
-    <t>0.8647,0.0023,0.0030,0.1262</t>
-  </si>
-  <si>
-    <t>0.9567,0.0022,0.0042,0.0142</t>
-  </si>
-  <si>
-    <t>0.8876,0.0014,0.0015,0.1593</t>
-  </si>
-  <si>
-    <t>0.9649,0.0034,0.0017,0.0174</t>
-  </si>
-  <si>
-    <t>0.9702,0.0047,0.0029,0.0032</t>
-  </si>
-  <si>
-    <t>0.9043,0.0100,0.0153,0.0284</t>
-  </si>
-  <si>
-    <t>0.9245,0.0090,0.0144,0.0105</t>
-  </si>
-  <si>
-    <t>0.9388,0.0014,0.0019,0.0612</t>
-  </si>
-  <si>
-    <t>0.9866,0.0014,0.0014,0.0017</t>
-  </si>
-  <si>
-    <t>0.9612,0.0042,0.0029,0.0107</t>
-  </si>
-  <si>
-    <t>0.9168,0.0158,0.0101,0.0165</t>
-  </si>
-  <si>
-    <t>0.9804,0.0006,0.0005,0.0125</t>
-  </si>
-  <si>
-    <t>0.8555,0.0183,0.2391,0.0029</t>
-  </si>
-  <si>
-    <t>0.9377,0.0019,0.0021,0.0517</t>
-  </si>
-  <si>
-    <t>0.0069,0.0185,0.9916,0.0003</t>
-  </si>
-  <si>
-    <t>0.4833,0.0244,0.6681,0.0031</t>
-  </si>
-  <si>
-    <t>0.8977,0.0044,0.0939,0.0033</t>
-  </si>
-  <si>
-    <t>0.3468,0.0611,0.7213,0.0004</t>
-  </si>
-  <si>
-    <t>0.9411,0.0041,0.0731,0.0004</t>
-  </si>
-  <si>
-    <t>0.0218,0.0032,0.9853,0.0014</t>
-  </si>
-  <si>
-    <t>0.5197,0.0097,0.6298,0.0020</t>
-  </si>
-  <si>
-    <t>0.9450,0.0051,0.0471,0.0018</t>
-  </si>
-  <si>
-    <t>0.8574,0.0038,0.1577,0.0043</t>
-  </si>
-  <si>
-    <t>0.9903,0.0001,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.9171,0.0099,0.0597,0.0020</t>
-  </si>
-  <si>
-    <t>0.9056,0.0164,0.0509,0.0029</t>
-  </si>
-  <si>
-    <t>0.9601,0.0039,0.0160,0.0021</t>
-  </si>
-  <si>
-    <t>0.9780,0.0015,0.0078,0.0015</t>
-  </si>
-  <si>
-    <t>0.9286,0.0021,0.0913,0.0011</t>
-  </si>
-  <si>
-    <t>0.9131,0.0348,0.0148,0.0106</t>
-  </si>
-  <si>
-    <t>0.6513,0.2608,0.0158,0.0054</t>
-  </si>
-  <si>
-    <t>0.9667,0.0109,0.0035,0.0025</t>
-  </si>
-  <si>
-    <t>0.8656,0.0076,0.0042,0.0641</t>
-  </si>
-  <si>
-    <t>0.9784,0.0020,0.0055,0.0020</t>
-  </si>
-  <si>
-    <t>0.9905,0.0011,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9947,0.0001,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9755,0.0011,0.0092,0.0018</t>
-  </si>
-  <si>
-    <t>0.9796,0.0014,0.0141,0.0002</t>
-  </si>
-  <si>
-    <t>0.9655,0.0009,0.0138,0.0018</t>
-  </si>
-  <si>
-    <t>0.5976,0.0281,0.4981,0.0020</t>
-  </si>
-  <si>
-    <t>0.8822,0.0073,0.1009,0.0038</t>
-  </si>
-  <si>
-    <t>0.6656,0.0259,0.4248,0.0018</t>
-  </si>
-  <si>
-    <t>0.8848,0.0007,0.1644,0.0005</t>
-  </si>
-  <si>
-    <t>0.9056,0.0049,0.1333,0.0006</t>
-  </si>
-  <si>
-    <t>0.9273,0.0033,0.0015,0.0509</t>
-  </si>
-  <si>
-    <t>0.9008,0.0168,0.0128,0.0145</t>
-  </si>
-  <si>
-    <t>0.7578,0.0113,0.0012,0.0575</t>
-  </si>
-  <si>
-    <t>0.9465,0.0046,0.0055,0.0217</t>
-  </si>
-  <si>
-    <t>0.8612,0.0079,0.0072,0.1117</t>
-  </si>
-  <si>
-    <t>0.9580,0.0012,0.0003,0.0296</t>
-  </si>
-  <si>
-    <t>0.9623,0.0048,0.0019,0.0089</t>
-  </si>
-  <si>
-    <t>0.8911,0.0084,0.0023,0.0393</t>
-  </si>
-  <si>
-    <t>0.9362,0.0027,0.0348,0.0067</t>
-  </si>
-  <si>
-    <t>0.9217,0.0099,0.0462,0.0079</t>
-  </si>
-  <si>
-    <t>0.9523,0.0036,0.0152,0.0106</t>
-  </si>
-  <si>
-    <t>0.0134,0.0082,0.9917,0.0001</t>
-  </si>
-  <si>
-    <t>0.0322,0.0312,0.9454,0.0021</t>
-  </si>
-  <si>
-    <t>0.8735,0.0078,0.1896,0.0015</t>
-  </si>
-  <si>
-    <t>0.0041,0.0152,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.8022,0.0043,0.2740,0.0019</t>
-  </si>
-  <si>
-    <t>0.0131,0.0034,0.9910,0.0006</t>
-  </si>
-  <si>
-    <t>0.7063,0.0055,0.4617,0.0012</t>
-  </si>
-  <si>
-    <t>0.9281,0.0033,0.0532,0.0036</t>
-  </si>
-  <si>
-    <t>0.9254,0.0041,0.0944,0.0017</t>
-  </si>
-  <si>
-    <t>0.9276,0.0021,0.0766,0.0023</t>
-  </si>
-  <si>
-    <t>0.9781,0.0005,0.0142,0.0006</t>
-  </si>
-  <si>
-    <t>0.8794,0.0151,0.0077,0.0476</t>
-  </si>
-  <si>
-    <t>0.9779,0.0008,0.0010,0.0131</t>
-  </si>
-  <si>
-    <t>0.9815,0.0012,0.0013,0.0088</t>
-  </si>
-  <si>
-    <t>0.9224,0.0018,0.0027,0.0774</t>
-  </si>
-  <si>
-    <t>0.9763,0.0007,0.0006,0.0173</t>
-  </si>
-  <si>
-    <t>0.9502,0.0039,0.0038,0.0285</t>
-  </si>
-  <si>
-    <t>0.9798,0.0003,0.0001,0.0215</t>
-  </si>
-  <si>
-    <t>0.9748,0.0016,0.0007,0.0091</t>
-  </si>
-  <si>
-    <t>0.4175,0.0663,0.6646,0.0035</t>
-  </si>
-  <si>
-    <t>0.1481,0.1122,0.8708,0.0008</t>
-  </si>
-  <si>
-    <t>0.7451,0.0036,0.5310,0.0002</t>
-  </si>
-  <si>
-    <t>0.8613,0.0127,0.1194,0.0021</t>
-  </si>
-  <si>
-    <t>0.3987,0.0030,0.8011,0.0004</t>
-  </si>
-  <si>
-    <t>0.4337,0.0012,0.6820,0.0027</t>
-  </si>
-  <si>
-    <t>0.8356,0.0079,0.2334,0.0032</t>
-  </si>
-  <si>
-    <t>0.0584,0.0099,0.9429,0.0014</t>
-  </si>
-  <si>
-    <t>0.9217,0.0001,0.0029,0.0423</t>
-  </si>
-  <si>
-    <t>0.9811,0.0002,0.0021,0.0029</t>
-  </si>
-  <si>
-    <t>0.9583,0.0002,0.0010,0.0350</t>
-  </si>
-  <si>
-    <t>0.5330,0.0001,0.0013,0.6367</t>
-  </si>
-  <si>
-    <t>0.6122,0.0001,0.0009,0.5835</t>
-  </si>
-  <si>
-    <t>0.8460,0.0032,0.1381,0.0040</t>
+    <t>0.9629,0.0017,0.0043,0.0206</t>
+  </si>
+  <si>
+    <t>0.0747,0.0012,0.0004,0.9770</t>
+  </si>
+  <si>
+    <t>0.9592,0.0031,0.0006,0.0346</t>
+  </si>
+  <si>
+    <t>0.1812,0.0066,0.0084,0.9125</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9932,0.0083,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0035,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9951,0.0047,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0035,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9530,0.0036,0.0555,0.0006</t>
+  </si>
+  <si>
+    <t>0.0862,0.0173,0.9204,0.0037</t>
+  </si>
+  <si>
+    <t>0.2590,0.0014,0.9187,0.0001</t>
+  </si>
+  <si>
+    <t>0.0301,0.0032,0.9724,0.0011</t>
+  </si>
+  <si>
+    <t>0.9386,0.0012,0.0900,0.0011</t>
+  </si>
+  <si>
+    <t>0.0012,0.9954,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0058,0.0005</t>
+  </si>
+  <si>
+    <t>0.0168,0.9759,0.0226,0.0014</t>
+  </si>
+  <si>
+    <t>0.0059,0.9903,0.0038,0.0015</t>
+  </si>
+  <si>
+    <t>0.0007,0.9984,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.8855,0.0061,0.0962,0.0078</t>
+  </si>
+  <si>
+    <t>0.1958,0.0059,0.8040,0.0087</t>
+  </si>
+  <si>
+    <t>0.0016,0.0009,0.9977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0161,0.0063,0.9630,0.0058</t>
+  </si>
+  <si>
+    <t>0.0247,0.0018,0.9838,0.0007</t>
+  </si>
+  <si>
+    <t>0.0063,0.0009,0.9914,0.0010</t>
+  </si>
+  <si>
+    <t>0.0012,0.0014,0.9972,0.0013</t>
+  </si>
+  <si>
+    <t>0.1140,0.8742,0.0371,0.0089</t>
+  </si>
+  <si>
+    <t>0.4925,0.5882,0.0105,0.0014</t>
+  </si>
+  <si>
+    <t>0.0023,0.0284,0.9955,0.0016</t>
+  </si>
+  <si>
+    <t>0.0021,0.5765,0.4145,0.0006</t>
+  </si>
+  <si>
+    <t>0.8119,0.1776,0.0421,0.0102</t>
+  </si>
+  <si>
+    <t>0.5041,0.1298,0.3330,0.0592</t>
+  </si>
+  <si>
+    <t>0.6364,0.4616,0.0023,0.0024</t>
+  </si>
+  <si>
+    <t>0.0110,0.9812,0.1323,0.0036</t>
+  </si>
+  <si>
+    <t>0.0152,0.8081,0.0993,0.0413</t>
+  </si>
+  <si>
+    <t>0.0092,0.0129,0.9822,0.0023</t>
+  </si>
+  <si>
+    <t>0.8059,0.0017,0.3268,0.0005</t>
+  </si>
+  <si>
+    <t>0.0164,0.0018,0.9796,0.0034</t>
+  </si>
+  <si>
+    <t>0.0789,0.3677,0.7002,0.0018</t>
+  </si>
+  <si>
+    <t>0.0019,0.9906,0.0039,0.0002</t>
+  </si>
+  <si>
+    <t>0.0019,0.0004,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0148,0.2755,0.0012,0.9306</t>
+  </si>
+  <si>
+    <t>0.0055,0.9729,0.0129,0.0300</t>
+  </si>
+  <si>
+    <t>0.0071,0.9892,0.0060,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0104,0.0003</t>
+  </si>
+  <si>
+    <t>0.0026,0.0217,0.9836,0.0036</t>
+  </si>
+  <si>
+    <t>0.0020,0.2120,0.9944,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.0028,0.9855,0.0031</t>
+  </si>
+  <si>
+    <t>0.0148,0.0015,0.9877,0.0007</t>
+  </si>
+  <si>
+    <t>0.0136,0.0092,0.9734,0.0014</t>
+  </si>
+  <si>
+    <t>0.0033,0.2631,0.9795,0.0023</t>
+  </si>
+  <si>
+    <t>0.9839,0.0170,0.0017,0.0012</t>
+  </si>
+  <si>
+    <t>0.9945,0.0020,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9851,0.0091,0.0022,0.0025</t>
+  </si>
+  <si>
+    <t>0.0026,0.0577,0.9929,0.0108</t>
+  </si>
+  <si>
+    <t>0.9915,0.0053,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9944,0.0032,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9916,0.0072,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0032,0.9048,0.9585,0.0016</t>
+  </si>
+  <si>
+    <t>0.0272,0.1224,0.9679,0.0022</t>
+  </si>
+  <si>
+    <t>0.0095,0.0079,0.9870,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.9680,0.9871,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.0012,0.9947,0.0010</t>
+  </si>
+  <si>
+    <t>0.0020,0.9966,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.9934,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9157,0.0097,0.1320,0.0026</t>
+  </si>
+  <si>
+    <t>0.5213,0.4924,0.0489,0.0045</t>
+  </si>
+  <si>
+    <t>0.0078,0.0028,0.9894,0.0052</t>
+  </si>
+  <si>
+    <t>0.0001,0.9465,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.9712,0.6535,0.0016</t>
+  </si>
+  <si>
+    <t>0.0029,0.9901,0.0109,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.9672,0.7632,0.0011</t>
+  </si>
+  <si>
+    <t>0.0041,0.0009,0.0056,0.9960</t>
+  </si>
+  <si>
+    <t>0.0010,0.0038,0.0009,0.9985</t>
+  </si>
+  <si>
+    <t>0.0135,0.0010,0.0001,0.9965</t>
+  </si>
+  <si>
+    <t>0.0150,0.0035,0.0009,0.9931</t>
+  </si>
+  <si>
+    <t>0.0292,0.0003,0.0008,0.9924</t>
+  </si>
+  <si>
+    <t>0.0093,0.0217,0.0039,0.9875</t>
+  </si>
+  <si>
+    <t>0.0002,0.9937,0.9513,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.5023,0.9928,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.9864,0.2777,0.0006</t>
+  </si>
+  <si>
+    <t>0.0121,0.6118,0.8592,0.0039</t>
+  </si>
+  <si>
+    <t>0.0008,0.9891,0.8046,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.9115,0.9794,0.0007</t>
+  </si>
+  <si>
+    <t>0.9950,0.0036,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9821,0.0111,0.0048,0.0021</t>
+  </si>
+  <si>
+    <t>0.9946,0.0028,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0016,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9964,0.0028,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9959,0.0017,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0019,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0013,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0002,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0016,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.1098,0.0027,0.9543,0.0006</t>
+  </si>
+  <si>
+    <t>0.3897,0.0063,0.6924,0.0053</t>
+  </si>
+  <si>
+    <t>0.9836,0.0009,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.0049,0.0004,0.9945,0.0004</t>
+  </si>
+  <si>
+    <t>0.0081,0.9877,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.0008,0.9977,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.0119,0.9793,0.0017,0.0059</t>
+  </si>
+  <si>
+    <t>0.0095,0.9824,0.0071,0.0008</t>
+  </si>
+  <si>
+    <t>0.0020,0.9964,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9953,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.2638,0.8142,0.0029,0.0009</t>
+  </si>
+  <si>
+    <t>0.8824,0.0349,0.0874,0.0130</t>
+  </si>
+  <si>
+    <t>0.1437,0.0070,0.9030,0.0020</t>
+  </si>
+  <si>
+    <t>0.2658,0.0698,0.6586,0.0305</t>
+  </si>
+  <si>
+    <t>0.6760,0.0292,0.3014,0.0228</t>
+  </si>
+  <si>
+    <t>0.0128,0.2189,0.0110,0.9283</t>
+  </si>
+  <si>
+    <t>0.0003,0.9985,0.0113,0.0004</t>
+  </si>
+  <si>
+    <t>0.0124,0.9733,0.0068,0.0109</t>
+  </si>
+  <si>
+    <t>0.0006,0.9948,0.0128,0.0037</t>
+  </si>
+  <si>
+    <t>0.0004,0.9948,0.7010,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.9950,0.0167,0.0020</t>
+  </si>
+  <si>
+    <t>0.9285,0.0917,0.0052,0.0005</t>
+  </si>
+  <si>
+    <t>0.5572,0.5358,0.0081,0.0027</t>
+  </si>
+  <si>
+    <t>0.9959,0.0012,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0004,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9941,0.0018,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9878,0.0094,0.0021,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9945,0.0020,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9884,0.0043,0.0045,0.0011</t>
+  </si>
+  <si>
+    <t>0.9893,0.0034,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.0020,0.7443,0.9900,0.0014</t>
+  </si>
+  <si>
+    <t>0.0013,0.9590,0.7752,0.0008</t>
+  </si>
+  <si>
+    <t>0.0060,0.0635,0.9726,0.0035</t>
+  </si>
+  <si>
+    <t>0.0806,0.1196,0.8582,0.0019</t>
+  </si>
+  <si>
+    <t>0.9416,0.0101,0.0462,0.0025</t>
+  </si>
+  <si>
+    <t>0.3403,0.0203,0.6708,0.0511</t>
+  </si>
+  <si>
+    <t>0.8242,0.0037,0.3304,0.0018</t>
+  </si>
+  <si>
+    <t>0.8584,0.0144,0.1100,0.0126</t>
+  </si>
+  <si>
+    <t>0.2428,0.0004,0.0005,0.9347</t>
+  </si>
+  <si>
+    <t>0.0001,0.0030,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0163,0.0007,0.0002,0.9958</t>
+  </si>
+  <si>
+    <t>0.0636,0.0005,0.0005,0.9867</t>
+  </si>
+  <si>
+    <t>0.0022,0.9503,0.8037,0.0005</t>
+  </si>
+  <si>
+    <t>0.9957,0.0016,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0158,0.9771,0.0043,0.0050</t>
+  </si>
+  <si>
+    <t>0.9903,0.0049,0.0011,0.0016</t>
+  </si>
+  <si>
+    <t>0.2741,0.7449,0.0164,0.0145</t>
+  </si>
+  <si>
+    <t>0.9864,0.0047,0.0050,0.0016</t>
+  </si>
+  <si>
+    <t>0.0435,0.0018,0.0049,0.9807</t>
+  </si>
+  <si>
+    <t>0.9904,0.0027,0.0044,0.0009</t>
+  </si>
+  <si>
+    <t>0.0500,0.1289,0.9262,0.0442</t>
+  </si>
+  <si>
+    <t>0.9606,0.0007,0.0014,0.0457</t>
+  </si>
+  <si>
+    <t>0.9857,0.0018,0.0009,0.0082</t>
+  </si>
+  <si>
+    <t>0.3046,0.7074,0.0085,0.0099</t>
+  </si>
+  <si>
+    <t>0.9818,0.0069,0.0038,0.0010</t>
+  </si>
+  <si>
+    <t>0.9052,0.0754,0.0121,0.0073</t>
+  </si>
+  <si>
+    <t>0.4757,0.4197,0.0959,0.0159</t>
+  </si>
+  <si>
+    <t>0.7831,0.1315,0.0595,0.0077</t>
+  </si>
+  <si>
+    <t>0.9292,0.0323,0.0427,0.0023</t>
+  </si>
+  <si>
+    <t>0.9931,0.0005,0.0018,0.0022</t>
+  </si>
+  <si>
+    <t>0.9964,0.0012,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0011,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9952,0.0001,0.0003,0.0031</t>
+  </si>
+  <si>
+    <t>0.9929,0.0035,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9960,0.0018,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9897,0.0059,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.8978,0.0765,0.0003,0.0066</t>
+  </si>
+  <si>
+    <t>0.6670,0.4911,0.0020,0.0024</t>
+  </si>
+  <si>
+    <t>0.8059,0.2645,0.0057,0.0022</t>
+  </si>
+  <si>
+    <t>0.0226,0.6517,0.8976,0.0056</t>
+  </si>
+  <si>
+    <t>0.9892,0.0152,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9406,0.0352,0.0196,0.0144</t>
+  </si>
+  <si>
+    <t>0.9958,0.0038,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9898,0.0159,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.0589,0.9964,0.0011</t>
+  </si>
+  <si>
+    <t>0.9696,0.0192,0.0058,0.0038</t>
+  </si>
+  <si>
+    <t>0.0017,0.0960,0.9880,0.0006</t>
+  </si>
+  <si>
+    <t>0.0046,0.1268,0.9883,0.0033</t>
+  </si>
+  <si>
+    <t>0.0543,0.0025,0.9617,0.0017</t>
+  </si>
+  <si>
+    <t>0.0091,0.0153,0.9919,0.0006</t>
+  </si>
+  <si>
+    <t>0.0013,0.0027,0.9972,0.0002</t>
+  </si>
+  <si>
+    <t>0.0023,0.0008,0.9971,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0011,0.9947,0.0012</t>
+  </si>
+  <si>
+    <t>0.0373,0.0408,0.9226,0.0155</t>
+  </si>
+  <si>
+    <t>0.1073,0.0355,0.8921,0.0036</t>
+  </si>
+  <si>
+    <t>0.7174,0.0234,0.3834,0.0040</t>
+  </si>
+  <si>
+    <t>0.1098,0.6142,0.4259,0.0078</t>
+  </si>
+  <si>
+    <t>0.1526,0.4334,0.3706,0.0017</t>
+  </si>
+  <si>
+    <t>0.6913,0.1799,0.1255,0.0049</t>
+  </si>
+  <si>
+    <t>0.6731,0.0419,0.2642,0.0336</t>
+  </si>
+  <si>
+    <t>0.2451,0.0533,0.7370,0.0119</t>
+  </si>
+  <si>
+    <t>0.6418,0.4591,0.0092,0.0015</t>
+  </si>
+  <si>
+    <t>0.8593,0.2522,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.7467,0.4068,0.0015,0.0013</t>
+  </si>
+  <si>
+    <t>0.9830,0.0227,0.0012,0.0010</t>
+  </si>
+  <si>
+    <t>0.9728,0.0413,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.0826,0.8185,0.1875,0.0173</t>
+  </si>
+  <si>
+    <t>0.9246,0.0034,0.0882,0.0032</t>
+  </si>
+  <si>
+    <t>0.8948,0.0020,0.0699,0.0068</t>
+  </si>
+  <si>
+    <t>0.9517,0.0014,0.0874,0.0007</t>
+  </si>
+  <si>
+    <t>0.6520,0.0141,0.2746,0.0293</t>
+  </si>
+  <si>
+    <t>0.0251,0.0016,0.9763,0.0026</t>
+  </si>
+  <si>
+    <t>0.0291,0.3748,0.8761,0.0248</t>
+  </si>
+  <si>
+    <t>0.0125,0.0142,0.9863,0.0012</t>
+  </si>
+  <si>
+    <t>0.0159,0.0087,0.9664,0.0010</t>
+  </si>
+  <si>
+    <t>0.0025,0.3182,0.8411,0.0018</t>
+  </si>
+  <si>
+    <t>0.9963,0.0026,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9801,0.0123,0.0073,0.0019</t>
+  </si>
+  <si>
+    <t>0.9945,0.0033,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9904,0.0055,0.0014,0.0017</t>
+  </si>
+  <si>
+    <t>0.9959,0.0017,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9971,0.0026,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0031,0.0515,0.9895,0.0032</t>
+  </si>
+  <si>
+    <t>0.0156,0.0541,0.9701,0.0043</t>
+  </si>
+  <si>
+    <t>0.6921,0.0064,0.2771,0.0201</t>
+  </si>
+  <si>
+    <t>0.0113,0.0133,0.9836,0.0012</t>
+  </si>
+  <si>
+    <t>0.0034,0.0015,0.9897,0.0029</t>
+  </si>
+  <si>
+    <t>0.0210,0.1868,0.9157,0.0011</t>
+  </si>
+  <si>
+    <t>0.0137,0.0064,0.9920,0.0001</t>
+  </si>
+  <si>
+    <t>0.0195,0.0050,0.9691,0.0021</t>
+  </si>
+  <si>
+    <t>0.0099,0.0056,0.9915,0.0005</t>
+  </si>
+  <si>
+    <t>0.0493,0.0099,0.9512,0.0020</t>
+  </si>
+  <si>
+    <t>0.0334,0.1236,0.8484,0.0139</t>
+  </si>
+  <si>
+    <t>0.7176,0.0272,0.2680,0.0450</t>
+  </si>
+  <si>
+    <t>0.9367,0.0023,0.0778,0.0017</t>
+  </si>
+  <si>
+    <t>0.8868,0.0014,0.0948,0.0057</t>
+  </si>
+  <si>
+    <t>0.9968,0.0032,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0009,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0016,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0052,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9945,0.0030,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0010,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.0283,0.3907,0.7039,0.0017</t>
+  </si>
+  <si>
+    <t>0.0034,0.0263,0.9772,0.0024</t>
+  </si>
+  <si>
+    <t>0.0031,0.0282,0.9916,0.0013</t>
+  </si>
+  <si>
+    <t>0.0621,0.1471,0.7449,0.0153</t>
+  </si>
+  <si>
+    <t>0.0022,0.0155,0.9928,0.0010</t>
+  </si>
+  <si>
+    <t>0.0994,0.0012,0.7252,0.0827</t>
+  </si>
+  <si>
+    <t>0.0744,0.0019,0.9359,0.0036</t>
+  </si>
+  <si>
+    <t>0.0188,0.0092,0.9062,0.0324</t>
+  </si>
+  <si>
+    <t>0.8375,0.0018,0.0027,0.2266</t>
+  </si>
+  <si>
+    <t>0.0586,0.0110,0.0015,0.9765</t>
+  </si>
+  <si>
+    <t>0.0736,0.0032,0.0008,0.9732</t>
+  </si>
+  <si>
+    <t>0.0034,0.0001,0.0003,0.9989</t>
+  </si>
+  <si>
+    <t>0.0077,0.0020,0.0002,0.9971</t>
+  </si>
+  <si>
+    <t>0.8608,0.0169,0.0009,0.0751</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
         <v>298</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3577,7 +3577,7 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
         <v>380</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3899,7 +3899,7 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
         <v>403</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4767,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
         <v>465</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
